--- a/data/trans_orig/IP40A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP40A-Habitat-trans_orig.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11166</t>
+          <t>10868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12764</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18505</t>
+          <t>18755</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13521</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>13311</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28169</t>
+          <t>28518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>14976</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29141</t>
+          <t>29747</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>20249</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35208</t>
+          <t>35997</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40215</t>
+          <t>40294</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60048</t>
+          <t>61129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36078</t>
+          <t>36680</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54451</t>
+          <t>54489</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44110</t>
+          <t>44164</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62598</t>
+          <t>62304</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>86390</t>
+          <t>86304</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>112311</t>
+          <t>110984</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,46%</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20302</t>
+          <t>20402</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35369</t>
+          <t>35681</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1444,12 +1444,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14577</t>
+          <t>15655</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29106</t>
+          <t>29735</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39053</t>
+          <t>38826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60252</t>
+          <t>60129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,71%</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9663</t>
+          <t>9621</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1993,12 +1993,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2028,12 +2028,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13991</t>
+          <t>14132</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2063,12 +2063,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -2091,12 +2091,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>877</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>11283</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17009</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2239,12 +2239,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>14395</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28598</t>
+          <t>28766</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2254,12 +2254,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22511</t>
+          <t>23163</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40284</t>
+          <t>40478</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2289,12 +2289,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>25763</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41832</t>
+          <t>41411</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2332,12 +2332,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26706</t>
+          <t>26618</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43797</t>
+          <t>43660</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2387,12 +2387,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56425</t>
+          <t>57456</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>79482</t>
+          <t>80803</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2402,12 +2402,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -2430,12 +2430,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59008</t>
+          <t>58593</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78781</t>
+          <t>78163</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2465,12 +2465,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58190</t>
+          <t>59673</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80240</t>
+          <t>80026</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>122119</t>
+          <t>122476</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>151358</t>
+          <t>151078</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,34%</t>
         </is>
       </c>
     </row>
@@ -2543,12 +2543,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22914</t>
+          <t>22544</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38688</t>
+          <t>38095</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25781</t>
+          <t>25682</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43044</t>
+          <t>42820</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52521</t>
+          <t>52338</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74827</t>
+          <t>75889</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2691,12 +2691,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13162</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6970</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18779</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>3177</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -3112,12 +3112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>681</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>9300</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4021</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13674</t>
+          <t>13433</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3197,12 +3197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -3225,12 +3225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11284</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16677</t>
+          <t>16041</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24437</t>
+          <t>23855</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -3338,12 +3338,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17125</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9553</t>
+          <t>9796</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>20998</t>
+          <t>21567</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>18897</t>
+          <t>19687</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>34424</t>
+          <t>34013</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -3451,12 +3451,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11899</t>
+          <t>11446</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24796</t>
+          <t>24110</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>17762</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30642</t>
+          <t>31903</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3501,42 +3501,42 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>14,24%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>25,59%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>41178</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>33251</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>50619</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>16,72%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>13,5%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>24,58%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>41178</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>32539</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>50620</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>16,72%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>41179</t>
+          <t>41146</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>57317</t>
+          <t>58693</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>30050</t>
+          <t>30053</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>47221</t>
+          <t>46963</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3634,12 +3634,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>75606</t>
+          <t>75050</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>99625</t>
+          <t>98550</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,0%</t>
         </is>
       </c>
     </row>
@@ -3677,12 +3677,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21544</t>
+          <t>22183</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>35599</t>
+          <t>36967</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15916</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30677</t>
+          <t>29905</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>41175</t>
+          <t>40529</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>61739</t>
+          <t>60151</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3790,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3805,12 +3805,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>12911</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19084</t>
+          <t>19254</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -3903,12 +3903,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>695</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -4246,12 +4246,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>730</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4261,12 +4261,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4281,12 +4281,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>9686</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -4359,12 +4359,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>18205</t>
+          <t>17957</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15400</t>
+          <t>15394</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>14601</t>
+          <t>14476</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>29608</t>
+          <t>29659</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -4472,12 +4472,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12140</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>25888</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>17179</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>31458</t>
+          <t>31700</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>33236</t>
+          <t>33187</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>54092</t>
+          <t>53248</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -4585,12 +4585,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>30496</t>
+          <t>29192</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>48838</t>
+          <t>48003</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>19689</t>
+          <t>19559</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>34620</t>
+          <t>34873</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>53761</t>
+          <t>52638</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>78018</t>
+          <t>76607</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -4698,12 +4698,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>45838</t>
+          <t>45802</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>67431</t>
+          <t>66859</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>34812</t>
+          <t>34996</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>53860</t>
+          <t>53242</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>86221</t>
+          <t>85486</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>115705</t>
+          <t>113286</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -4811,12 +4811,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>18798</t>
+          <t>18627</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>34684</t>
+          <t>35399</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4846,12 +4846,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>19523</t>
+          <t>19719</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>35761</t>
+          <t>35656</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4881,12 +4881,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>41936</t>
+          <t>41606</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>64880</t>
+          <t>65137</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4959,12 +4959,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>13052</t>
+          <t>12942</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4994,12 +4994,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>20822</t>
+          <t>21926</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4741</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -5267,12 +5267,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>897</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -5380,12 +5380,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>16628</t>
+          <t>16787</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5395,12 +5395,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>9843</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>22231</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>18324</t>
+          <t>18556</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>35441</t>
+          <t>35398</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>18960</t>
+          <t>19514</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>36676</t>
+          <t>36074</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>17633</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>33551</t>
+          <t>33167</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>41751</t>
+          <t>39757</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>64566</t>
+          <t>62276</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -5606,12 +5606,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>42003</t>
+          <t>41733</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>65192</t>
+          <t>65308</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5641,12 +5641,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>56115</t>
+          <t>54857</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>80891</t>
+          <t>79890</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>103353</t>
+          <t>101356</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>137419</t>
+          <t>135742</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -5719,12 +5719,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>96196</t>
+          <t>95905</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>127006</t>
+          <t>125975</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5734,12 +5734,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>98328</t>
+          <t>96014</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>128825</t>
+          <t>128125</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>202841</t>
+          <t>201771</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>245738</t>
+          <t>245662</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -5832,12 +5832,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>201539</t>
+          <t>198937</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>240665</t>
+          <t>237181</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5847,12 +5847,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>185901</t>
+          <t>185699</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>221666</t>
+          <t>223984</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>395200</t>
+          <t>394895</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>448965</t>
+          <t>447175</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -5945,12 +5945,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>97103</t>
+          <t>94676</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>126932</t>
+          <t>127466</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>89383</t>
+          <t>89393</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>120016</t>
+          <t>121063</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>196288</t>
+          <t>194631</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>239807</t>
+          <t>237737</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -6058,12 +6058,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>25429</t>
+          <t>25561</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>17844</t>
+          <t>17280</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>34730</t>
+          <t>34791</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>31858</t>
+          <t>32018</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>52564</t>
+          <t>52626</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -6171,12 +6171,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>9535</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>14308</t>
+          <t>14226</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5964</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -6859,12 +6859,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11783</t>
+          <t>11399</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -6972,12 +6972,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>12608</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17406</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12332</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25882</t>
+          <t>26622</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -7085,12 +7085,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>11603</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25132</t>
+          <t>24335</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15090</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29115</t>
+          <t>28769</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29925</t>
+          <t>30159</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49484</t>
+          <t>48653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -7198,12 +7198,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30990</t>
+          <t>30738</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47748</t>
+          <t>47914</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31856</t>
+          <t>31087</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48051</t>
+          <t>48910</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>65587</t>
+          <t>67065</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>89944</t>
+          <t>91006</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>41,27%</t>
         </is>
       </c>
     </row>
@@ -7311,12 +7311,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>20554</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35468</t>
+          <t>36563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7326,12 +7326,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24046</t>
+          <t>23771</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40764</t>
+          <t>40482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7361,12 +7361,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48779</t>
+          <t>47655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71049</t>
+          <t>70500</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7396,12 +7396,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -7424,12 +7424,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10266</t>
+          <t>10502</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13045</t>
+          <t>13331</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7474,12 +7474,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8414</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20064</t>
+          <t>20008</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7509,12 +7509,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -7537,12 +7537,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>584</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6408</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7622,12 +7622,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -7880,12 +7880,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>11772</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7965,12 +7965,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -7993,12 +7993,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11989</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8043,12 +8043,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14068</t>
+          <t>14279</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -8106,12 +8106,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19585</t>
+          <t>19266</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20792</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8156,12 +8156,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20929</t>
+          <t>20565</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37054</t>
+          <t>36496</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22059</t>
+          <t>21678</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36237</t>
+          <t>36612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27176</t>
+          <t>27847</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45313</t>
+          <t>44919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54119</t>
+          <t>54353</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>77605</t>
+          <t>77130</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -8332,12 +8332,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41838</t>
+          <t>42685</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60531</t>
+          <t>60632</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8367,12 +8367,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47256</t>
+          <t>47024</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67796</t>
+          <t>67563</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94485</t>
+          <t>94704</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>121785</t>
+          <t>121696</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -8445,12 +8445,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33437</t>
+          <t>34114</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51794</t>
+          <t>51746</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8460,12 +8460,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8480,12 +8480,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41305</t>
+          <t>41628</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60946</t>
+          <t>62263</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80204</t>
+          <t>79594</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>106623</t>
+          <t>106808</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -8558,12 +8558,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17985</t>
+          <t>18806</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8573,12 +8573,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8593,12 +8593,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7089</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18443</t>
+          <t>18633</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17027</t>
+          <t>17831</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>31412</t>
+          <t>32410</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -8671,12 +8671,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8686,12 +8686,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6671</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -9127,12 +9127,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10524</t>
+          <t>11032</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11522</t>
+          <t>10679</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18182</t>
+          <t>18099</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -9240,12 +9240,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15978</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>18978</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>16027</t>
+          <t>14984</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>32136</t>
+          <t>29208</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -9353,12 +9353,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17860</t>
+          <t>17809</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>31412</t>
+          <t>32641</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9368,12 +9368,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16406</t>
+          <t>15809</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30596</t>
+          <t>30181</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>37735</t>
+          <t>36670</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>57220</t>
+          <t>57049</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -9466,12 +9466,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28573</t>
+          <t>29252</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>44710</t>
+          <t>45781</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>32448</t>
+          <t>32622</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>50456</t>
+          <t>50084</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>66490</t>
+          <t>66155</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>88830</t>
+          <t>88055</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -9579,12 +9579,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>34151</t>
+          <t>33879</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>49865</t>
+          <t>50522</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32961</t>
+          <t>32590</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>51075</t>
+          <t>49486</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9629,12 +9629,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>72334</t>
+          <t>71431</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>95272</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9664,12 +9664,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -9692,12 +9692,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9727,12 +9727,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16057</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9742,12 +9742,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9762,12 +9762,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>12179</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>26478</t>
+          <t>25874</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9777,12 +9777,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -9805,12 +9805,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>569</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9875,12 +9875,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>7170</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9895,7 +9895,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -10040,7 +10040,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -10148,12 +10148,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9884</t>
+          <t>10776</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10183,12 +10183,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>7945</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10198,12 +10198,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>15172</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -10261,12 +10261,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13661</t>
+          <t>13816</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14576</t>
+          <t>15785</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10311,12 +10311,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10331,12 +10331,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>11691</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>24735</t>
+          <t>25195</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10346,12 +10346,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -10374,12 +10374,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12377</t>
+          <t>12343</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26203</t>
+          <t>27476</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>14188</t>
+          <t>13664</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>27548</t>
+          <t>27514</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10424,12 +10424,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10444,12 +10444,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>30156</t>
+          <t>30869</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>50879</t>
+          <t>49640</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10459,12 +10459,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -10487,12 +10487,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14704</t>
+          <t>15084</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>28949</t>
+          <t>29305</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>20222</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>36995</t>
+          <t>37056</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -10537,12 +10537,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -10557,12 +10557,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>39423</t>
+          <t>38221</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>60266</t>
+          <t>59921</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10572,12 +10572,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -10600,12 +10600,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>39660</t>
+          <t>39397</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>59414</t>
+          <t>59682</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>40045</t>
+          <t>38917</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>58669</t>
+          <t>58577</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10650,12 +10650,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>84415</t>
+          <t>85681</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>111747</t>
+          <t>111974</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10685,12 +10685,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -10713,12 +10713,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>28141</t>
+          <t>28182</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>45454</t>
+          <t>46364</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10728,12 +10728,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>20452</t>
+          <t>19993</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>36066</t>
+          <t>35507</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>53540</t>
+          <t>52324</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>76205</t>
+          <t>76728</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -10826,12 +10826,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>12858</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10841,12 +10841,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10861,12 +10861,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>8687</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>20044</t>
+          <t>20695</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>15132</t>
+          <t>15416</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>29808</t>
+          <t>30344</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -10939,12 +10939,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>10391</t>
+          <t>9508</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10954,12 +10954,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10974,12 +10974,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>15557</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -11169,12 +11169,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>640</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11239,12 +11239,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>749</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -11282,12 +11282,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>15102</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -11297,12 +11297,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -11317,12 +11317,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -11332,12 +11332,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>14031</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>29407</t>
+          <t>30111</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -11367,12 +11367,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -11395,12 +11395,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>12576</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>27061</t>
+          <t>26762</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11410,12 +11410,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11430,12 +11430,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>17458</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>34230</t>
+          <t>34413</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>34131</t>
+          <t>34992</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>56290</t>
+          <t>55499</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -11508,12 +11508,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>40592</t>
+          <t>40751</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>62437</t>
+          <t>61818</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11523,12 +11523,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11543,12 +11543,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>46125</t>
+          <t>46273</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>70151</t>
+          <t>70543</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>91944</t>
+          <t>93199</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>125962</t>
+          <t>126014</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -11621,12 +11621,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>77985</t>
+          <t>78569</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>106561</t>
+          <t>105691</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11636,12 +11636,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>94111</t>
+          <t>93099</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>123676</t>
+          <t>124571</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>179414</t>
+          <t>179569</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>221789</t>
+          <t>223157</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -11734,12 +11734,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>157338</t>
+          <t>159078</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>192822</t>
+          <t>193423</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11749,12 +11749,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>168403</t>
+          <t>167059</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>204945</t>
+          <t>202418</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>336395</t>
+          <t>337893</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>386624</t>
+          <t>388769</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -11847,12 +11847,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>130426</t>
+          <t>131495</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>163272</t>
+          <t>164304</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11862,12 +11862,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11882,12 +11882,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>134099</t>
+          <t>133631</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>169600</t>
+          <t>169380</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>275220</t>
+          <t>275038</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>321464</t>
+          <t>322625</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -11960,12 +11960,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>25978</t>
+          <t>26320</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>45029</t>
+          <t>43406</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -11975,12 +11975,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>33540</t>
+          <t>34749</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>54808</t>
+          <t>54999</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>65303</t>
+          <t>63427</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>93595</t>
+          <t>93209</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -12073,12 +12073,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>6179</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>17500</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12088,12 +12088,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12108,12 +12108,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>12490</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>12271</t>
+          <t>11695</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>25245</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
